--- a/public/crawlability-qilates-september-2026.xlsx
+++ b/public/crawlability-qilates-september-2026.xlsx
@@ -510,14 +510,14 @@
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות (הבולטת: https://www.qilates.co.il/articles/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>app.qilates.co.il: להגדיר noindex.</t>
         </is>
       </c>
     </row>
@@ -525,14 +525,14 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת (הבולטת: http://www.qilates.co.il/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות (הבולטת: https://www.qilates.co.il/articles/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>app.qilates.co.il: להגדיר noindex.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת (הבולטת: http://www.qilates.co.il/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-qilates-september-2026.xlsx
+++ b/public/crawlability-qilates-september-2026.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות (הבולטת: https://www.qilates.co.il/articles/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 3 כתובות; הבולטת https://www.qilates.co.il/articles/ (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת (הבולטת: http://www.qilates.co.il/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת; הבולטת http://www.qilates.co.il/ (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-qilates-september-2026.xlsx
+++ b/public/crawlability-qilates-september-2026.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר 36 כתובות שמפנות (301/302) ולהשאיר את כתובות היעד בלבד.</t>
+          <t>להסיר ממפת האתר 36 כתובות שמפנות (301/302) (באתר WordPress/Yoast: להעביר את העמודים המפנים לטיוטה או להחריגם מה-sitemap; המפה נוצרת אוטומטית).</t>
         </is>
       </c>
     </row>
